--- a/www/download/COUNTRY.RUS.EXI382.xlsx
+++ b/www/download/COUNTRY.RUS.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>Rússia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17533435582822</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17399079754601</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>67.494</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>59.564</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>59.621</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>59.122</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>58.458</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>62.938</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>65.068</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>65.119</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>66.655</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>66.426</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>62.442</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>68.162</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>68.851</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>70.556</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>67.063</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>69.253</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>69.78</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>64.318</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>71.516</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>72.949</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>63.596</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>51.166</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>48.122</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>57.525</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>57.025</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>61.474</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>62.596</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>63.434</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>57.08</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>57.159</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>56.397</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>55.782</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>56.11</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>58.51</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>59.847</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>61.476</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>61.516</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>57.391</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>62.866</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>65.368</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>62.035</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>64.094</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>64.978</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>59.316</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>66.571</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>68.351</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>59.304</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>47.705</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>45.094</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>53.848</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>53.744</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>57.63</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>58.712</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>133596.86</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>115795.261</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>116025.048</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>115261.266</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>113918.698</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>122096.354</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>126353.905</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>127011.144</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>130152.309</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>130040.446</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>122555.317</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>133616.965</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>134998.125</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>138570.733</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>131892.914</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>136096.775</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>138156.604</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>128580.35</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>141511.214</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>144139.741</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>125727.187</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>101139.112</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>95055.001</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>113851.361</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>112698.467</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>121659.064</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>123886.883</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>125819.217</t>
+          <t>229000606927.982</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>106112.071</t>
+          <t>147420609038.195</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>106402.489</t>
+          <t>172115591379.505</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>104563.688</t>
+          <t>147151148171.04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>103401.592</t>
+          <t>153248436084.411</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>96937.194</t>
+          <t>166863650595.304</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>102256.503</t>
+          <t>177405298159.858</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>107285.466</t>
+          <t>150691746068.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>110757.119</t>
+          <t>160470321633.342</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>111603.658</t>
+          <t>169209494897.014</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>103534.079</t>
+          <t>159396564438.212</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>113821.915</t>
+          <t>170020101539.868</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>115532.259</t>
+          <t>164661028108.235</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>119140.747</t>
+          <t>180668049292.768</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>112582.512</t>
+          <t>167257359517.265</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>116548.748</t>
+          <t>166634721246.058</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>119701.33</t>
+          <t>184052135020.237</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>109476.638</t>
+          <t>166617304126.971</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>122684.004</t>
+          <t>179833580374.37</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>135370.034</t>
+          <t>177969688143.988</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>117564.097</t>
+          <t>147489289175.11</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>94573.966</t>
+          <t>120549718580.781</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>89302.92</t>
+          <t>123595827606.353</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>106839.526</t>
+          <t>139802459983.087</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>106448.721</t>
+          <t>147260137748.7</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>114332.347</t>
+          <t>154780504688.654</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>116475.636</t>
+          <t>156118635902.334</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>73861778598.58</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>31951036474.2561</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>50846821125.3572</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>43119690952.3018</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>40312688840.1415</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>54034286753.8841</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>51979848781.3553</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>45378033651.4232</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>45881851984.038</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>44457826870.8298</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>50328738132.6054</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>51931406501.5054</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>48786679180.0326</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>47860333538.1908</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>42793663349.1032</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>58627474681.7847</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>61146383435.1978</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>70155351160.7798</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>68496552753.5427</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>69281324890.3309</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>53708202364.7654</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>42441817307.1822</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>51573061124.7527</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>58473519761.2512</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>59595923551.921</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>65626056002.1175</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>54018076651.7782</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>149170103.394264</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>35869705.968947</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>35634046.0553828</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>47313780.6347884</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>56979430.0045545</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>43572761.4344714</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>37661143.4957597</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>33576080.7521703</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>33632144.3488023</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>28064955.5938021</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>22242804.7966864</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16714082.4299125</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>13445619.2714641</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>12844239.7480085</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>15486606.4960799</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10622812.5990147</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>11169932.0993751</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>8267621.95641382</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8952300.44172704</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>24266162.7570739</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>25686200.097905</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>23716272.9833902</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>22355451.7257493</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22738160.5880976</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>20007798.872771</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>24034292.020685</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>29138719.2102243</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>300964.807258739</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>638222.281758151</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>664354.338894303</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>636072.410391628</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>677739.804921049</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>920468.162478458</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>942422.901495472</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>826506.356652088</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>807591.55280361</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>810708.500296652</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>788681.278375357</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>932720.926097616</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>948760.818240766</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>974675.674195379</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>935148.374891104</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1072005.78021561</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1150168.35456443</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1099179.02597127</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1261112.44317386</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1320064.38731366</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>1268829.96080439</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>944779.593996536</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>967397.83828792</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1089080.01775149</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1206357.10503309</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>1182078.28939763</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1182295.87759609</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>853623.267298206</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1120259.88570103</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1424536.03763024</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1252100.44094228</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1375449.89862218</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1790248.9820772</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1911143.1886743</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1573619.15933541</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1539356.74088862</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1586241.175781</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1601899.09457723</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1827768.78102094</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1833980.06548426</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2021948.19518732</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1875816.22541765</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2155146.79437909</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2478135.14365976</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2476157.92533795</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2610640.35453778</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2674215.03996918</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2503504.89587058</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1865077.46926571</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021668.1559872</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2224041.10104442</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2496040.29945961</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2495751.59527638</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2471461.06979628</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.703441478416062</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.32108384294554</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.0926084786635</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.42496376227923</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.56498871633282</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.793994143783566</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.967233560646593</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.36425991536276</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.41396356534507</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.5103264341788</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.05715626581399</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.19177416264832</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.3681107413288</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.48934217946711</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.63082202338238</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.987954429772111</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.95761913093137</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.560488775105722</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.791097494226754</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.953918087712722</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.18894119971227</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.22832037260462</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.731580759339142</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.827143746798229</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.786174538973234</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.742179156104377</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.15623442079333</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1164.38623531856</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>559.756911753241</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>889.566510413264</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>764.567417922911</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>722.684039807659</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>963.004641835885</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>888.392561636259</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>758.234057704217</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>746.336413403547</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>722.703473418789</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>876.944784593742</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>826.065066991893</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>766.845004401694</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>732.167628475631</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>689.829843896898</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>914.715091838699</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>941.039335696038</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1182.74107213724</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1028.93252647235</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1013.60829592164</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>905.636810695379</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>889.663780554927</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1143.6705762776</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1085.90548395946</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1108.87671518476</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1138.74060961946</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>920.051677884162</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>84815790911.733</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1272291065.73849</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>29484368171.9193</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>26335733683.7822</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>19370971297.4211</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>35510573874.7339</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>29375056452.8664</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>23151681395.9171</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>26317132620.7746</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>34906334548.3566</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>36203190940.933</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>42341522695.5441</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>33802813790.5799</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>46734939224.5144</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>33603016354.9447</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>49945631271.639</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>57419409495.8439</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>64233472135.4919</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>59099084489.7523</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>56259195874.4562</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>36759307931.4766</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>36400190244.4814</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>43441219047.3708</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>53415691543.0547</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>51009198706.9218</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>57319842988.9203</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>52385317770.7472</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>91195730809.8064</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3315921154.667</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>30959482607.7234</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>27290718045.8346</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20194003663.6648</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>36380126560.9229</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>31079811531.6311</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>25762222933.0766</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>28470816863.509</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>36308505804.449</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>37764508081.4242</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>42918810650.5123</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>34550541885.9711</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>47380529313.9544</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>35810890080.8709</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>51929714130.4156</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>59061133335.5828</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>66320146670.1019</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>61607305775.926</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>59007269900.4041</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>39352296032.1061</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>39894331990.9905</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>47438883284.9482</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>57119656509.5495</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>55001157544.9584</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>61752595403.3105</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>58024821187.432</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-6379939898.07337</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-2043630088.92852</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1475114435.80412</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-954984362.052441</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-823032366.243725</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-869552686.188987</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1704755078.76463</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-2610541537.15949</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-2153684242.73439</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-1402171256.09238</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-1561317140.49127</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-577287954.968266</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-747728095.39124</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-645590089.439941</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-2207873725.92621</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-1984082858.77666</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-1641723839.73891</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-2086674534.60992</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-2508221286.17368</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-2748074025.94796</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-2592988100.62949</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-3494141746.50915</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-3997664237.5774</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-3703964966.49474</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-3991958838.03666</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-4432752414.39025</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-5639503416.68483</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>1983.46381013836</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1858.99963560078</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>1861.5144220259</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>1854.04828228246</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>1853.67640758046</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>1727.62468788997</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>1747.67566227965</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>1792.66238909293</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>1801.62890944648</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>1814.22163339602</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1804.01245839992</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1810.54807049919</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.669</t>
+          <t>1815.97389185798</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1822.61576000479</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1814.81954571039</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.036</t>
+          <t>1818.41191880014</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>1842.19660651751</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.957</t>
+          <t>1845.65416692667</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1842.91846989303</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.602</t>
+          <t>1980.50758325696</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>1982.38572690714</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>1.965</t>
+          <t>1982.45592697899</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2.418</t>
+          <t>1980.3579649046</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>1984.10541463043</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2.619</t>
+          <t>1980.64735552329</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2.673</t>
+          <t>1983.89015428861</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>1983.84709676249</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>1979.40063013045</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1944.06081902396</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>1946.04983495729</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1949.54291281495</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1948.73059073296</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1939.94343648739</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1941.87174667714</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>1950.44678204565</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>1952.62634461085</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>1957.67094560703</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1962.70646359852</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1960.28527625361</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>1960.72575456322</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>1963.97948582763</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>1966.70460120419</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>1965.20841666305</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>1979.89395211776</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>1999.11922697205</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>1978.72672383794</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>1975.89444558754</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>1976.97380043544</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>1976.66908822908</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>1975.30507167732</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>1979.14613109805</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1976.29488264148</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1979.02137987918</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>1979.16004598592</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>110214.815213363</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>102304.45989616</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>109734.652337899</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>95770.377368024</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>100089.853468875</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>156957.358625628</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>157992.974954528</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>162559.503751118</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>166894.423470553</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>202902.308912287</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>268908.925396257</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>330780.81813114</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>354188.538351476</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>424533.905169514</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>299574.316342647</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>413483.472370545</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>508460.54991869</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>572946.720137008</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>552349.993929289</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>520372.135061027</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>440624.112408042</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>371969.020103796</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>455741.629269236</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>549035.532049579</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>543067.02190126</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>563244.908911007</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>582245.918229117</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>43091177069.9847</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>17736929392.4935</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>26166839770.8155</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>27358986579.4268</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>34517373478.8951</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>38960716703.2398</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>33110351627.9651</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>30241220132.1705</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>29835338620.7066</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>32379206155.9849</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>32077195056.2572</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>30021098402.598</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>24679396864.3925</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>26744605940.471</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>23913840465.2089</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>23071591950.8319</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>26705112755.1989</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>25069168219.5314</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>26307398740.0733</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>23752279661.9996</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>21349959086.7334</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>17114346116.4565</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>17448448912.2108</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>22157485539.7613</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>21592341208.3068</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>23543407470.9488</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>25132552791.4305</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>96730.3131689884</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>85250.0328297198</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>99496.0747790623</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>74218.6995760304</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>59124.733782178</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>83526.8137589256</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>101769.379549139</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>110990.687259582</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>110704.12145642</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>127126.325498081</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>159417.427300374</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>199525.403595034</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>246135.502051318</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>290298.409031047</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>215438.536823811</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>293000.395758431</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>353214.403614081</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>423145.552827597</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>430352.142917947</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>390194.154511472</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>311329.314900712</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>293178.18448257</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>358460.495523619</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>363396.260415469</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>391804.5410647</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>406703.479899143</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>418174.322166856</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>133596.86</t>
+          <t>120267643744.313</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>115795.261</t>
+          <t>15544817420.2649</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>116025.048</t>
+          <t>53734671982.258</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>115261.266</t>
+          <t>49634420362.669</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>113918.698</t>
+          <t>46373543749.6653</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>122096.354</t>
+          <t>63079233376.5233</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>126353.905</t>
+          <t>53417723480.7483</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>127011.144</t>
+          <t>44763708356.684</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>130152.309</t>
+          <t>46606994383.9443</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>130040.446</t>
+          <t>53388995105.1614</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>122555.317</t>
+          <t>49967868962.9408</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>133616.965</t>
+          <t>52832904888.3869</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>134998.125</t>
+          <t>45063924845.769</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>138570.733</t>
+          <t>55084000101.4537</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>131892.914</t>
+          <t>45132792802.6432</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>136096.775</t>
+          <t>58161416935.9588</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>138156.604</t>
+          <t>66222195631.4288</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>128580.35</t>
+          <t>72969634596.4068</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>141511.214</t>
+          <t>71431195473.5355</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>144139.741</t>
+          <t>66172763089.2819</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>125727.187</t>
+          <t>45611000492.6506</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>101139.112</t>
+          <t>45158253601.9741</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>95055.001</t>
+          <t>51519280950.8745</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>113851.361</t>
+          <t>57122544424.2921</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>112698.467</t>
+          <t>58796205649.3917</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>121659.064</t>
+          <t>65672262547.7541</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>123886.883</t>
+          <t>61531542460.8629</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>125819.217</t>
+          <t>13484.5020443743</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>106112.071</t>
+          <t>17054.4270664407</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>106402.489</t>
+          <t>10238.5775588368</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>104563.688</t>
+          <t>21551.6777919936</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>103401.592</t>
+          <t>40965.1196866973</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>96937.194</t>
+          <t>73430.5448667025</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>102256.503</t>
+          <t>56223.5954053889</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>107285.466</t>
+          <t>51568.8164915358</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>110757.119</t>
+          <t>56190.3020141324</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>111603.658</t>
+          <t>75775.9834142059</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>103534.079</t>
+          <t>109491.498095884</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>113821.915</t>
+          <t>131255.414536107</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>115532.259</t>
+          <t>108053.036300159</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>119140.747</t>
+          <t>134235.496138467</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>112582.512</t>
+          <t>84135.7795188358</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>116548.748</t>
+          <t>120483.076612115</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>119701.33</t>
+          <t>155246.14630461</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>109476.638</t>
+          <t>149801.167309411</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>122684.004</t>
+          <t>121997.851011342</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>135370.034</t>
+          <t>130177.980549555</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>117564.097</t>
+          <t>129294.797507331</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>94573.966</t>
+          <t>78790.8356212266</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>89302.92</t>
+          <t>97281.1337456171</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>106839.526</t>
+          <t>185639.271634111</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>106448.721</t>
+          <t>151262.48083656</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>114332.347</t>
+          <t>156541.429011864</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>116475.636</t>
+          <t>164071.596062261</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>173547.693</t>
+          <t>-77176466674.3283</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>124634.05</t>
+          <t>2192111972.22853</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>138815.116</t>
+          <t>-27567832211.4424</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>120218.104</t>
+          <t>-22275433783.2422</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>124242.849</t>
+          <t>-11856170270.7702</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>137252.761</t>
+          <t>-24118516673.2835</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>144356.866</t>
+          <t>-20307371852.7832</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>124470.952</t>
+          <t>-14522488224.5134</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>131398.163</t>
+          <t>-16771655763.2377</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>137872.689</t>
+          <t>-21009788949.1765</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>129732.237</t>
+          <t>-17890673906.6836</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>138346.73</t>
+          <t>-22811806485.7889</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>134533.424</t>
+          <t>-20384527981.3764</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>145124.35</t>
+          <t>-28339394160.9827</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>133982.015</t>
+          <t>-21218952337.4342</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>134276.078</t>
+          <t>-35089824985.1269</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>146174.18</t>
+          <t>-39517082876.2299</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>132137.281</t>
+          <t>-47900466376.8754</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>143653.904</t>
+          <t>-45123796733.4621</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>142818.71</t>
+          <t>-42420483427.2823</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>119544.788</t>
+          <t>-24261041405.9171</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>97299.25</t>
+          <t>-28043907485.5176</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>99397.778</t>
+          <t>-34070832038.6637</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>112955.188</t>
+          <t>-34965058884.5308</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>118145.9</t>
+          <t>-37203864441.0849</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>124162.506</t>
+          <t>-42128855076.8052</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>124924.77</t>
+          <t>-36398989669.4324</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>133586.961652205</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>135574.50352336</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>145457.332550962</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>104984.711507252</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>73511.6467781265</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>103431.976381614</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>125543.601158639</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>130162.908657874</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>133463.765354921</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>190964.32806921</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>260810.574242594</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>365529.987494201</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>394270.867713933</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.427</t>
+          <t>466890.16144464</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>376040.011280406</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>480041.640591969</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.717</t>
+          <t>576350.2704104</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.713</t>
+          <t>741835.199824351</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.811</t>
+          <t>844541.982203296</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.849</t>
+          <t>674127.511330065</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>1.728</t>
+          <t>537967.339230376</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>527368.709342785</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>615068.071790506</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>625352.78510487</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.672</t>
+          <t>656970.197500953</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>1.674</t>
+          <t>667946.410711044</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1.652</t>
+          <t>677060.193233014</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>80739.509</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>83986.867</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>80268.759</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>74753.416</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>75511.704</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>85794.032</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>87482.098</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>79147.286</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>84187.422</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>86480.907</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>78477.531</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>86762.236</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>85183.004</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>87090.635</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>83382.607</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>82886.876</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>85423.485</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>73962.264</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>86871.547</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>87850.619</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>74750.734</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>61066.05</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>59142.415</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>68459.196</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>71172.053</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>73309.649</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>74683.928</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>138224.983470056</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>137496.934365713</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>162004.477452287</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>111120.178401951</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>77514.4575075868</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>112700.889398815</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>151149.009950818</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>173786.239921343</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>175617.355441242</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>213988.258229026</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>306300.738239569</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>399507.213130329</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>484728.458440722</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>536314.628175413</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>437003.827754598</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>615277.487280096</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>786099.342887222</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>979521.940230206</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1020568.32182278</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>897308.923035122</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>717140.805364426</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>648536.955965353</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>818540.105204264</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>771408.666763632</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>877862.585904995</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>893356.611552459</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>855034.2893792</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>64854.462</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>32815.193</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>48096.999</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>40604.44</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>37926.433</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>51740.992</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>49698.46</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>43970.979</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>44779.044</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>42402.997</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>48331.34</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>50609.385</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>48049.779</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>46934.85</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>41577.541</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>56220.049</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>57624.149</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>66441.953</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>64967.029</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>66081.347</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>51433.012</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>40919.807</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>49470.657</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>56413.137</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>56961.681</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>62608.236</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>52066.878</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>223.36</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>121.22</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>157.52</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>172.64</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>87.35</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>105.75</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>143.99</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>147.34</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>163.2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>114.22</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>124.9</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>140.44</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>153.84</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>170.78</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>107.31</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>107.73</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>64.77</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>88.84</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>104.85</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>128.58</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>131.12</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>80.52</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>89.39</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>86.88</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>82.62</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>123.7</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>164.135</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>40.181</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>38.245</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>51.672</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>61.288</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>47.525</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>41.246</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>36.916</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>36.581</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>30.785</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>24.242</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>18.275</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>14.822</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>13.895</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>11.474</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>11.952</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>8.866</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>9.607</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>27.575</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>29.205</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>26.993</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>25.334</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>25.755</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>22.609</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>27.087</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>32.758</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>167010.808793524</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>173244.732258693</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>204723.146599294</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>136907.448496386</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>111408.855446154</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>178649.283422806</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>214035.511379895</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>221876.303241473</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>239540.948067946</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>301382.8778893</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>365395.266162604</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>445180.890215124</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>552070.574728549</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>689477.91653072</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>527554.663722794</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>656108.013011189</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>828020.007248848</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>909978.107634006</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>862205.245137946</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>807494.251441106</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>641071.528772968</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>612346.988937617</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>721642.659450651</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>788261.896565854</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>796103.420118945</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>812438.121382876</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>866230.549312258</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>125819217334.405</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>106112071000.016</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>106402489000.009</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>104563688000.011</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>103401591999.999</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>96937193999.99</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>102256503000.017</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>107285466000.042</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>110757119000.023</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>111603657999.989</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>103534079000.001</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>113821914999.987</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>115532258999.997</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>119140746999.983</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>112582512000.032</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>116548748000.006</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>119701330000.008</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>109476637999.997</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>122684004000.041</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>135370033843.919</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>117564096918.719</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>94573966155.9576</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>89302920343.8432</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>106839525985.053</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>106448721275.037</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>114332346864.228</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>116475636221.617</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>133596859953.673</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>115795261000.013</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>116025048000.012</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>115261266000.014</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>113918697999.995</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>122096353999.996</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>126353905000.005</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>127011144000.025</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>130152309000.035</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>130040445999.987</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>122555316999.988</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>133616964999.982</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>134998125000.002</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>138570732999.99</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>131892914000.025</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>136096775000.012</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>138156604000.006</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>128580349999.996</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>141511214000.038</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>144139741245.498</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>125727186696.913</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>101139111524.291</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>95055000803.0034</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>113851361375.712</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>112698467077.717</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>121659063746.742</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>123886882741.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>80739509062.7692</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>83986866511.4751</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>80268759023.1491</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>74753416298.3044</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>75511703683.5337</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>85794031660.1638</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>87482098056.9528</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>79147286229.6637</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>84187422437.2154</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>86480907152.3252</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>78477531222.3691</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>86762236126.4411</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>85183004276.0493</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>87090635244.331</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>83382607433.3707</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>82886875653.3383</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>85423485410.7543</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>73962263951.8224</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>86871546866.4309</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>87850619276.64</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>74750734185.4211</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>61066050099.2417</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>59142414690.4101</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>68459195978.2495</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>71172053391.8285</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>73309649309.9521</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>74683927616.3342</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>67493592.7169372</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>59563599.9999983</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>59620799.9999952</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>59122199.9999927</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>58457899.9999932</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>62938100.0000046</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>65068100.0000216</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>65118999.9999972</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>66654999.9999995</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>66426099.9999999</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>62441999.999984</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>68161999.9999917</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>68851099.9999974</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>70556099.9999936</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>67062899.9999636</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>69253100.0000023</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>69779800.0000097</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>64318499.9999971</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>71516300.0000139</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>72949109.9928861</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>63595777.8849782</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>51166435.5589747</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>48121681.1346957</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>57525495.2561516</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>57025127.2052509</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>61474355.4484334</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>62595686.9896836</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>63434087.7263739</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>57080199.9999977</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>57159099.9999937</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>56397499.9999927</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>55781899.9999927</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>56110100.0000087</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>58510000.00002</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>59846999.9999986</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>61476100.0000002</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>61515999.9999995</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>57390999.999984</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>62865999.9999916</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>63619999.9999958</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>65367999.9999942</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>62035099.9999633</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>64093700.0000029</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>64977500.000009</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>59315899.9999952</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>66570500.0000148</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>68351181.782047</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>59304349.967319</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>47705457.0893165</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>45094332.401741</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>53847706.4762979</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>53744408.85612</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>57630381.7109396</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>58712002.7605441</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>133596859953.673</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>115795261000.013</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>116025048000.012</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>115261266000.014</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>113918697999.995</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>122096353999.996</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>126353905000.005</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>127011144000.025</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>130152309000.035</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>130040445999.987</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>122555316999.988</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>133616964999.982</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>134998125000.002</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>138570732999.99</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>131892914000.025</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>136096775000.012</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>138156604000.006</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>128580349999.996</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>141511214000.038</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>144139741245.498</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>125727186696.913</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>101139111524.291</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>95055000803.0034</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>113851361375.712</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>112698467077.717</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>121659063746.742</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>123886882741.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>125819217334.405</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>106112071000.016</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>106402489000.009</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>104563688000.011</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>103401591999.999</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>96937193999.99</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>102256503000.017</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>107285466000.042</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>110757119000.023</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>111603657999.989</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>103534079000.001</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>113821914999.987</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>115532258999.997</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>119140746999.983</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>112582512000.032</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>116548748000.006</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>119701330000.008</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>109476637999.997</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>122684004000.041</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>135370033843.919</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>117564096918.719</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>94573966155.9576</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>89302920343.8432</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>106839525985.053</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>106448721275.037</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>114332346864.228</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>116475636221.617</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>670398.361125671</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>671723.582196104</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>752926.355621792</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>514462.415146878</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>399854.676811498</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>595717.91525172</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>750674.130685232</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>782871.039381222</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>807104.095999502</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>962940.365959055</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1222135.7512964</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1563639.72829133</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1925139.94910544</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2243222.51701126</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1760160.00211961</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2346944.56341929</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2846383.91183475</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3401405.95236824</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3375975.11967139</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2987528.65616858</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2458986.13013098</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2255760.37371771</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2776697.60365345</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2761816.99118426</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>3012192.49075943</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>3074789.80186403</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>3104956.00354163</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>186096.750801606</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>186936.311061584</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>210433.638066164</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>143863.569920791</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>103068.299945539</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>148237.495486873</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>184703.574018861</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>202103.02001229</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>202824.213055286</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>254154.589915118</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>351648.876255723</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>471501.763210428</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>551081.452750938</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>623741.16259472</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>494817.806263085</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>681107.841629221</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>868218.624124367</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1065926.29669767</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1117376.18813037</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>972560.085746336</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>771644.870330704</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>712003.956420926</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>878092.329401981</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>837912.452138994</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>939413.939071316</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>955627.928425286</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>946091.34632861</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
